--- a/public/template-trabajadores-agrisoft.xlsx
+++ b/public/template-trabajadores-agrisoft.xlsx
@@ -3,23 +3,25 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="trabajadores" sheetId="1" r:id="rId4"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">trabajadores!$A$1:$AA$9</definedName>
+  </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
-  <si>
-    <t>rut</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="88">
+  <si>
+    <t>Rut</t>
   </si>
   <si>
     <t>Nombre</t>
   </si>
   <si>
-    <t>Apellido paterno</t>
+    <t>Apellido</t>
   </si>
   <si>
     <t>Apellido materno</t>
@@ -46,27 +48,192 @@
     <t>Teléfono</t>
   </si>
   <si>
+    <t>Correo</t>
+  </si>
+  <si>
     <t>Teléfono empresa</t>
   </si>
   <si>
     <t>Fecha de ingreso</t>
   </si>
   <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>Contratista</t>
+  </si>
+  <si>
+    <t>Cuadrilla</t>
+  </si>
+  <si>
+    <t>Líder de Cuadrilla</t>
+  </si>
+  <si>
+    <t>Turno</t>
+  </si>
+  <si>
+    <t>Pulsera</t>
+  </si>
+  <si>
+    <t>Observación</t>
+  </si>
+  <si>
+    <t>Banco</t>
+  </si>
+  <si>
+    <t>Tipo de cuenta</t>
+  </si>
+  <si>
+    <t>Número de cuenta</t>
+  </si>
+  <si>
+    <t>AFP</t>
+  </si>
+  <si>
+    <t>Salud</t>
+  </si>
+  <si>
     <t>status</t>
   </si>
   <si>
-    <t>11.111.111-1</t>
-  </si>
-  <si>
-    <t>Apellido</t>
-  </si>
-  <si>
-    <t>Apellido 2</t>
+    <t>59.029.140-4</t>
+  </si>
+  <si>
+    <t>Juan</t>
+  </si>
+  <si>
+    <t>Peréz</t>
+  </si>
+  <si>
+    <t>Rojas</t>
+  </si>
+  <si>
+    <t>1985-05-15</t>
+  </si>
+  <si>
+    <t>Femenino</t>
+  </si>
+  <si>
+    <t>Casado</t>
+  </si>
+  <si>
+    <t>XIII</t>
+  </si>
+  <si>
+    <t>Santiago</t>
+  </si>
+  <si>
+    <t>Avenida 456</t>
+  </si>
+  <si>
+    <t>+56950171534</t>
+  </si>
+  <si>
+    <t>m.paillalef.c@gmail.com</t>
+  </si>
+  <si>
+    <t>876543210</t>
+  </si>
+  <si>
+    <t>2019-06-15</t>
+  </si>
+  <si>
+    <t>Cosechero</t>
+  </si>
+  <si>
+    <t>Cuadrilla 1</t>
+  </si>
+  <si>
+    <t>Turno Mañana</t>
+  </si>
+  <si>
+    <t>1A2B3C4D</t>
+  </si>
+  <si>
+    <t>Ingreso trabajador 9:50 por lejanía</t>
+  </si>
+  <si>
+    <t>Banco de Chile</t>
+  </si>
+  <si>
+    <t>Cuenta Corriente</t>
+  </si>
+  <si>
+    <t>000010687709</t>
+  </si>
+  <si>
+    <t>AFP Provida</t>
+  </si>
+  <si>
+    <t>Fonasa</t>
+  </si>
+  <si>
+    <t>Activo</t>
+  </si>
+  <si>
+    <t>59.029.940-5</t>
+  </si>
+  <si>
+    <t>Roberto</t>
+  </si>
+  <si>
+    <t>Martinez</t>
+  </si>
+  <si>
+    <t>1992-03-22</t>
   </si>
   <si>
     <t>Masculino</t>
   </si>
   <si>
+    <t>VIII</t>
+  </si>
+  <si>
+    <t>Concepción</t>
+  </si>
+  <si>
+    <t>Calle 789</t>
+  </si>
+  <si>
+    <t>+56957911082</t>
+  </si>
+  <si>
+    <t>daniela.marchant.toledo@gmail.com</t>
+  </si>
+  <si>
+    <t>765432109</t>
+  </si>
+  <si>
+    <t>2020-08-20</t>
+  </si>
+  <si>
+    <t>Turno Tarde</t>
+  </si>
+  <si>
+    <t>98798798A</t>
+  </si>
+  <si>
+    <t>Banco Santander</t>
+  </si>
+  <si>
+    <t>Cuenta Vista</t>
+  </si>
+  <si>
+    <t>AFP Habitat</t>
+  </si>
+  <si>
+    <t>Isapre Vida Tres</t>
+  </si>
+  <si>
+    <t>59.051.480-2</t>
+  </si>
+  <si>
+    <t>Pedro</t>
+  </si>
+  <si>
+    <t>1968-01-24</t>
+  </si>
+  <si>
     <t>Soltero</t>
   </si>
   <si>
@@ -77,35 +244,62 @@
   </si>
   <si>
     <t>Pasaje 19</t>
+  </si>
+  <si>
+    <t>kinetick@gmail.com</t>
+  </si>
+  <si>
+    <t>98765432</t>
+  </si>
+  <si>
+    <t>2023-12-31</t>
+  </si>
+  <si>
+    <t>Cuadrilla 2</t>
+  </si>
+  <si>
+    <t>098098900000a</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Banco Estado</t>
+  </si>
+  <si>
+    <t>Cuenta RUT</t>
+  </si>
+  <si>
+    <t>AFP Uno</t>
+  </si>
+  <si>
+    <t>Isapre Nueva Más Vida</t>
+  </si>
+  <si>
+    <t>Inactivo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy/mm/dd"/>
-  </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="12.0"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -122,14 +316,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="164" xfId="0" applyFont="1" applyNumberFormat="1"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -160,40 +360,40 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Aptos Narrow"/>
-        <a:ea typeface="Aptos Narrow"/>
-        <a:cs typeface="Aptos Narrow"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow"/>
-        <a:ea typeface="Aptos Narrow"/>
-        <a:cs typeface="Aptos Narrow"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -344,24 +544,36 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="11.22" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.67"/>
-    <col customWidth="1" min="2" max="2" width="7.22"/>
-    <col customWidth="1" min="3" max="3" width="13.78"/>
-    <col customWidth="1" min="4" max="4" width="14.22"/>
-    <col customWidth="1" min="5" max="5" width="17.44"/>
-    <col customWidth="1" min="6" max="6" width="11.11"/>
-    <col customWidth="1" min="7" max="7" width="9.89"/>
-    <col customWidth="1" min="8" max="8" width="6.44"/>
-    <col customWidth="1" min="9" max="9" width="6.56"/>
-    <col customWidth="1" min="10" max="10" width="8.78"/>
-    <col customWidth="1" min="11" max="11" width="9.78"/>
-    <col customWidth="1" min="12" max="12" width="15.0"/>
-    <col customWidth="1" min="13" max="13" width="14.67"/>
-    <col customWidth="1" min="14" max="14" width="5.67"/>
-    <col customWidth="1" min="15" max="26" width="10.56"/>
+    <col customWidth="1" min="1" max="1" width="10.44"/>
+    <col customWidth="1" min="2" max="2" width="9.11"/>
+    <col customWidth="1" min="3" max="3" width="9.22"/>
+    <col customWidth="1" min="4" max="4" width="16.0"/>
+    <col customWidth="1" min="5" max="5" width="18.33"/>
+    <col customWidth="1" min="6" max="6" width="12.89"/>
+    <col customWidth="1" min="7" max="7" width="11.33"/>
+    <col customWidth="1" min="8" max="8" width="8.0"/>
+    <col customWidth="1" min="9" max="9" width="9.33"/>
+    <col customWidth="1" min="10" max="10" width="10.0"/>
+    <col customWidth="1" min="11" max="11" width="11.67"/>
+    <col customWidth="1" min="12" max="12" width="27.67"/>
+    <col customWidth="1" min="13" max="13" width="16.22"/>
+    <col customWidth="1" min="14" max="14" width="15.44"/>
+    <col customWidth="1" min="15" max="15" width="8.44"/>
+    <col customWidth="1" min="16" max="16" width="11.22"/>
+    <col customWidth="1" min="17" max="17" width="9.67"/>
+    <col customWidth="1" min="18" max="18" width="16.0"/>
+    <col customWidth="1" min="19" max="19" width="11.44"/>
+    <col customWidth="1" min="20" max="20" width="12.56"/>
+    <col customWidth="1" min="21" max="21" width="25.89"/>
+    <col customWidth="1" min="22" max="22" width="17.67"/>
+    <col customWidth="1" min="23" max="23" width="17.78"/>
+    <col customWidth="1" min="24" max="24" width="16.78"/>
+    <col customWidth="1" min="25" max="25" width="14.0"/>
+    <col customWidth="1" min="26" max="26" width="21.89"/>
+    <col customWidth="1" min="27" max="27" width="11.11"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
+    <row r="1" ht="24.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,64 +615,276 @@
       </c>
       <c r="N1" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="2">
-        <v>24838.0</v>
+        <v>27</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>31</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>19</v>
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>34</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="1">
-        <v>9.87654321E8</v>
-      </c>
-      <c r="L2" s="1">
-        <v>9.8765432E7</v>
-      </c>
-      <c r="M2" s="2">
-        <v>45292.0</v>
-      </c>
-      <c r="N2" s="3">
-        <v>1.0</v>
+        <v>36</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="X2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z2" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA2" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
-      <c r="E3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="A3" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="X3" s="3">
+        <v>9.8029383202E10</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="E4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="A4" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="X4" s="5">
+        <v>9.8239823982E10</v>
+      </c>
+      <c r="Y4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>87</v>
+      </c>
     </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="E5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
+    <row r="5" ht="15.75" customHeight="1"/>
     <row r="6" ht="15.75" customHeight="1"/>
     <row r="7" ht="15.75" customHeight="1"/>
     <row r="8" ht="15.75" customHeight="1"/>
@@ -1457,23 +1881,39 @@
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
+  <autoFilter ref="$A$1:$AA$9"/>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" prompt="Haz clic e introduce un valor, 0 es inactivo y 1 es activo" sqref="N2">
-      <formula1>"1,0"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="AA2:AA4">
+      <formula1>"Activo,Inactivo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2">
-      <formula1>"I,II,III,IV,V,VI,VII,VIII,IX,X,XI,XII,XIII,XIV,XV,XVI"</formula1>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Z2:Z4">
+      <formula1>"Fonasa,Isapre Banmédica,Isapre Colmena,Isapre Consalud,Isapre Cruz Blanca,Isapre Nueva Más Vida,Isapre Vida Tres,Isapre Masvida,Isapre Río Blanco,Isapre Colmena Golden Cross"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2:F4">
+      <formula1>"Femenino,Masculino,Otro"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="V2:V4">
+      <formula1>"Banco de Chile,Banco Estado,Banco Santander,Banco BCI,Banco Itaú,Banco Falabella,Banco Scotiabank,Banco Security,Banco Ripley,Banco Consorcio,Banco Internacional,Banco Corpbanca,Banco BICE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="Y2:Y4">
+      <formula1>"AFP Capital,AFP Cuprum,AFP Habitat,AFP Modelo,AFP Planvital,AFP Provida,AFP Uno,AFP Magister"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="W2:W4">
+      <formula1>"Cuenta Corriente,Cuenta Vista,Cuenta de Ahorro,Cuenta RUT"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="H2:H4">
+      <formula1>"I,II,III,IV,V,VI,VII,VIII,IX,X,XI,XII,XIII,XIV,XV"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G2:G4">
       <formula1>"Casado,Soltero,Divorciado,Viudo"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F2">
-      <formula1>"Masculino,Femenino,Otro"</formula1>
-    </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="L4"/>
+  </hyperlinks>
   <printOptions/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>